--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_73_R8.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_73_R8.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0911</v>
+        <v>4.2057</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8783</v>
+        <v>3.1273</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2128</v>
+        <v>1.0784</v>
       </c>
       <c r="G2" t="n">
         <v>2.9386</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9955000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0093</v>
+        <v>1.2584</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0139</v>
+        <v>-1.1483</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9304</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. SORKIN</t>
+          <t>M. SANTOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7549</v>
+        <v>3.0013</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4595</v>
+        <v>2.4512</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2954</v>
+        <v>0.5501</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.286</v>
+        <v>1.95</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.6808</v>
+        <v>0.6484</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3948</v>
+        <v>1.3016</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.0604</v>
+        <v>1.3354</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.7759</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.2845</v>
+        <v>1.2514</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2256</v>
+        <v>0.6146</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9049</v>
+        <v>0.5644</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6793</v>
+        <v>0.0502</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7573</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>1.628</v>
+        <v>-0.0982</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8707</v>
+        <v>-0.7088</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8919</v>
+        <v>0.9304</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8919</v>
+        <v>1.214</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. SANTOS</t>
+          <t>R. SORKIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5734</v>
+        <v>1.9367</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2586</v>
+        <v>1.7085</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3148</v>
+        <v>0.2282</v>
       </c>
       <c r="G4" t="n">
-        <v>1.95</v>
+        <v>-1.286</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6484</v>
+        <v>-1.6808</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3016</v>
+        <v>0.3948</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3354</v>
+        <v>-1.0604</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08400000000000001</v>
+        <v>-0.7759</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2514</v>
+        <v>-0.2845</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6146</v>
+        <v>-0.2256</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5644</v>
+        <v>-0.9049</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0502</v>
+        <v>0.6793</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2349</v>
+        <v>-0.0608</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2908</v>
+        <v>0.8771</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9441000000000001</v>
+        <v>-0.9379</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9304</v>
+        <v>1.8919</v>
       </c>
       <c r="W4" t="n">
-        <v>1.214</v>
+        <v>1.8919</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. OMORUYI</t>
+          <t>J. DOWTIN JR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3675</v>
+        <v>0.5926</v>
       </c>
       <c r="E5" t="n">
-        <v>0.953</v>
+        <v>-2.2266</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5855</v>
+        <v>2.8192</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5379</v>
+        <v>-1.1386</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1164</v>
+        <v>-0.8441</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4216</v>
+        <v>-0.2946</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08400000000000001</v>
+        <v>-2.8537</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08400000000000001</v>
+        <v>-0.7255</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-2.1283</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.622</v>
+        <v>1.7151</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2004</v>
+        <v>-0.1186</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4216</v>
+        <v>1.8337</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.3195</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9054</v>
+        <v>0.0354</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8689</v>
+        <v>1.109</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0365</v>
+        <v>-1.0736</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1726</v>
+        <v>0.584</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3491</v>
+        <v>-0.0385</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>1.402</v>
@@ -922,13 +922,13 @@
         <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2473</v>
+        <v>0.1641</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5702</v>
+        <v>0.8808</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8175</v>
+        <v>-0.7167</v>
       </c>
       <c r="V6" t="n">
         <v>-1.214</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. DOWTIN JR</t>
+          <t>C. OMORUYI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2063</v>
+        <v>0.098</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8911</v>
+        <v>0.7171</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6848</v>
+        <v>-0.6191</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1386</v>
+        <v>-0.5379</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8441</v>
+        <v>-0.1164</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2946</v>
+        <v>-0.4216</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.8537</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7255</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.1283</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.7151</v>
+        <v>-0.622</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1186</v>
+        <v>-0.2004</v>
       </c>
       <c r="O7" t="n">
-        <v>1.8337</v>
+        <v>-0.4216</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3195</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7635</v>
+        <v>0.6359</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4446</v>
+        <v>0.633</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.2081</v>
+        <v>0.0029</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4601</v>
+        <v>-1.3421</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1368</v>
+        <v>-0.0189</v>
       </c>
       <c r="F8" t="n">
         <v>-1.3232</v>
@@ -1078,10 +1078,10 @@
         <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5386</v>
+        <v>-0.4206</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="U8" t="n">
         <v>-0.3145</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. HOARD</t>
+          <t>L. WALKER IV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6592</v>
+        <v>-2.4337</v>
       </c>
       <c r="E9" t="n">
-        <v>2.441</v>
+        <v>0.5453</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.1002</v>
+        <v>-2.979</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7644</v>
+        <v>-2.7199</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1091</v>
+        <v>-4.8043</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3447</v>
+        <v>2.0844</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1134</v>
+        <v>0.1364</v>
       </c>
       <c r="K9" t="n">
-        <v>0.397</v>
+        <v>-3.3198</v>
       </c>
       <c r="L9" t="n">
-        <v>1.7164</v>
+        <v>3.4561</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.8778</v>
+        <v>-2.8563</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5061</v>
+        <v>-1.4845</v>
       </c>
       <c r="O9" t="n">
         <v>-1.3717</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5515</v>
+        <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1748</v>
+        <v>-1.3917</v>
       </c>
       <c r="T9" t="n">
-        <v>2.0568</v>
+        <v>0.0712</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.882</v>
+        <v>-1.4629</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1418</v>
+        <v>1.214</v>
       </c>
       <c r="W9" t="n">
-        <v>1.7501</v>
+        <v>1.4975</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.8919</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. WALKER IV</t>
+          <t>J. HOARD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3176</v>
+        <v>-2.5789</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.473</v>
+        <v>1.4541</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8446</v>
+        <v>-4.033</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.7199</v>
+        <v>-0.7644</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.8043</v>
+        <v>-1.1091</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0844</v>
+        <v>0.3447</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1364</v>
+        <v>2.1134</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.3198</v>
+        <v>0.397</v>
       </c>
       <c r="L10" t="n">
-        <v>3.4561</v>
+        <v>1.7164</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.8563</v>
+        <v>-2.8778</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4845</v>
+        <v>-1.5061</v>
       </c>
       <c r="O10" t="n">
         <v>-1.3717</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6237</v>
+        <v>2.5515</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.2756</v>
+        <v>-0.7448</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9471000000000001</v>
+        <v>1.0699</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3284</v>
+        <v>-1.8147</v>
       </c>
       <c r="V10" t="n">
-        <v>1.214</v>
+        <v>-0.1418</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4975</v>
+        <v>1.7501</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2836</v>
+        <v>-1.8919</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4091</v>
+        <v>-4.9223</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6437</v>
+        <v>-2.0225</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7653</v>
+        <v>-2.8998</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5971</v>
@@ -1312,13 +1312,13 @@
         <v>2.3195</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.1341</v>
+        <v>-1.6474</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2355</v>
+        <v>0.3857</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.8986</v>
+        <v>-2.0331</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6778999999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0188</v>
+        <v>-5.5059</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7067</v>
+        <v>-3.1603</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.312</v>
+        <v>-2.3457</v>
       </c>
       <c r="G12" t="n">
         <v>-1.4937</v>
@@ -1390,13 +1390,13 @@
         <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8112</v>
+        <v>-1.2984</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6484</v>
+        <v>-0.1019</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1628</v>
+        <v>-1.1964</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3943</v>
@@ -1423,31 +1423,31 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.111600000000001</v>
+        <v>-6.364599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>1.789999999999998</v>
+        <v>2.5367</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.901299999999999</v>
+        <v>-8.901399999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-4.5602</v>
       </c>
       <c r="H13" t="n">
-        <v>-9.027199999999999</v>
+        <v>-9.027200000000001</v>
       </c>
       <c r="I13" t="n">
         <v>4.466799999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2857999999999997</v>
+        <v>-0.2857999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.5343</v>
+        <v>-4.534300000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>4.2484</v>
+        <v>4.248400000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-4.2745</v>
@@ -1468,13 +1468,13 @@
         <v>16.2367</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.1722</v>
+        <v>-5.4253</v>
       </c>
       <c r="T13" t="n">
-        <v>5.232</v>
+        <v>5.9789</v>
       </c>
       <c r="U13" t="n">
-        <v>-11.4041</v>
+        <v>-11.404</v>
       </c>
       <c r="V13" t="n">
         <v>0.1418</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. IZUNDU</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.787</v>
+        <v>3.5791</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2773</v>
+        <v>2.9343</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4904</v>
+        <v>0.6449</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9477</v>
+        <v>4.0605</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1618</v>
+        <v>3.5252</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.214</v>
+        <v>0.5352</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0692</v>
+        <v>4.0747</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0692</v>
+        <v>2.7433</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.3314</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1215</v>
+        <v>-0.0142</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0926</v>
+        <v>0.7819</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.214</v>
+        <v>-0.7961</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1598</v>
+        <v>-3.7112</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6279</v>
+        <v>1.2325</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8704</v>
+        <v>1.3568</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2425</v>
+        <v>-0.1243</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.7886</v>
+        <v>0.1418</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4975</v>
+        <v>1.214</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.2862</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5188</v>
+        <v>3.1251</v>
       </c>
       <c r="E15" t="n">
         <v>2.2236</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2952</v>
+        <v>0.9014</v>
       </c>
       <c r="G15" t="n">
         <v>1.3024</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7345</v>
+        <v>1.3407</v>
       </c>
       <c r="T15" t="n">
         <v>1.5534</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8188</v>
+        <v>-0.2126</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6778999999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8965</v>
+        <v>2.3188</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5495</v>
+        <v>1.9033</v>
       </c>
       <c r="F16" t="n">
-        <v>0.347</v>
+        <v>0.4155</v>
       </c>
       <c r="G16" t="n">
         <v>0.7643</v>
@@ -1702,13 +1702,13 @@
         <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>1.382</v>
+        <v>1.8044</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1483</v>
+        <v>1.5022</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2337</v>
+        <v>0.3023</v>
       </c>
       <c r="V16" t="n">
         <v>0.6778999999999999</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. DOBRIC</t>
+          <t>S. MILJENOVIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8442</v>
+        <v>2.1564</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3998</v>
+        <v>1.7155</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4444</v>
+        <v>0.4409</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8413</v>
+        <v>0.6921</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9785</v>
+        <v>0.8092</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1372</v>
+        <v>-0.1171</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4419</v>
+        <v>1.6211</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0469</v>
+        <v>0.3697</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3949</v>
+        <v>1.2514</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2832</v>
+        <v>-0.929</v>
       </c>
       <c r="N17" t="n">
-        <v>1.0254</v>
+        <v>0.4395</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2578</v>
+        <v>-1.3684</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0029</v>
+        <v>0.284</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2334</v>
+        <v>0.0944</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.2305</v>
+        <v>0.1896</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2525</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>O. DOBRIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8441</v>
+        <v>1.9451</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8727</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0286</v>
+        <v>2.017</v>
       </c>
       <c r="G18" t="n">
-        <v>4.0605</v>
+        <v>0.8413</v>
       </c>
       <c r="H18" t="n">
-        <v>3.5252</v>
+        <v>0.9785</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5352</v>
+        <v>-0.1372</v>
       </c>
       <c r="J18" t="n">
-        <v>4.0747</v>
+        <v>-0.4419</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7433</v>
+        <v>-0.0469</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3314</v>
+        <v>-0.3949</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0142</v>
+        <v>1.2832</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7819</v>
+        <v>1.0254</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7961</v>
+        <v>0.2578</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.8556</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.7112</v>
+        <v>-1.3917</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5026</v>
+        <v>1.1037</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2952</v>
+        <v>1.7616</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7978</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. MILJENOVIC</t>
+          <t>E. IZUNDU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7297</v>
+        <v>1.4566</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4796</v>
+        <v>2.744</v>
       </c>
       <c r="F19" t="n">
-        <v>0.25</v>
+        <v>-1.2874</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6921</v>
+        <v>0.9477</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8092</v>
+        <v>1.1618</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1171</v>
+        <v>-0.214</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6211</v>
+        <v>1.0692</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3697</v>
+        <v>1.0692</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2514</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.929</v>
+        <v>-0.1215</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4395</v>
+        <v>0.0926</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3684</v>
+        <v>-0.214</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1428</v>
+        <v>1.2975</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1415</v>
+        <v>1.337</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0013</v>
+        <v>-0.0395</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2525</v>
+        <v>-0.7886</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.4975</v>
       </c>
       <c r="X19" t="n">
-        <v>0.2525</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9074</v>
+        <v>1.0261</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0075</v>
+        <v>0.3464</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9149</v>
+        <v>0.6797</v>
       </c>
       <c r="G20" t="n">
         <v>0.4747</v>
@@ -2014,13 +2014,13 @@
         <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2008</v>
+        <v>0.3194</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0747</v>
+        <v>0.2792</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2754</v>
+        <v>0.0402</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. KALINIC</t>
+          <t>Y. DOS SANTOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0667</v>
+        <v>0.5471</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0082</v>
+        <v>0.4919</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9415</v>
+        <v>0.0552</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2255</v>
+        <v>-0.5764</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4275</v>
+        <v>-0.4693</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.653</v>
+        <v>-0.1071</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1431</v>
+        <v>0.2244</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9278</v>
+        <v>0.0672</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.0709</v>
+        <v>0.1571</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0824</v>
+        <v>-0.8008</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4997</v>
+        <v>-0.5365</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5821</v>
+        <v>-0.2643</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1092</v>
+        <v>0.4277</v>
       </c>
       <c r="T21" t="n">
-        <v>2.3986</v>
+        <v>0.2675</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.2893</v>
+        <v>0.1601</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1107</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.9615</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Y. DOS SANTOS</t>
+          <t>S. OJELEYE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2843</v>
+        <v>-0.001</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2158</v>
+        <v>-0.0735</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5764</v>
+        <v>-0.9058</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4693</v>
+        <v>-0.1931</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1071</v>
+        <v>-0.7127</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2244</v>
+        <v>-1.1309</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0672</v>
+        <v>-0.7359</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1571</v>
+        <v>-0.3949</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8008</v>
+        <v>0.225</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5365</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2643</v>
+        <v>-0.3178</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6959</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4037</v>
+        <v>0.2939</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4402</v>
+        <v>0.7866</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0365</v>
+        <v>-0.4927</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2.0026</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.8223</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. OJELEYE</t>
+          <t>N. KALINIC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3999</v>
+        <v>-0.0862</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1914</v>
+        <v>-0.0534</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2085</v>
+        <v>-0.0328</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9058</v>
+        <v>-0.2255</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1931</v>
+        <v>1.4275</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7127</v>
+        <v>-1.653</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1309</v>
+        <v>-0.1431</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7359</v>
+        <v>0.9278</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.3949</v>
+        <v>-1.0709</v>
       </c>
       <c r="M23" t="n">
-        <v>0.225</v>
+        <v>-0.0824</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.4997</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3178</v>
+        <v>-0.5821</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3917</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.5515</v>
+        <v>-2.3195</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.105</v>
+        <v>0.9564</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6686</v>
+        <v>1.337</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7736</v>
+        <v>-0.3806</v>
       </c>
       <c r="V23" t="n">
-        <v>2.0026</v>
+        <v>0.1107</v>
       </c>
       <c r="W23" t="n">
-        <v>2.8223</v>
+        <v>1.0722</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.8197</v>
+        <v>-0.9615</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0884</v>
+        <v>-1.5043</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0022</v>
+        <v>-0.7663</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0862</v>
+        <v>-0.738</v>
       </c>
       <c r="G24" t="n">
         <v>-1.5462</v>
@@ -2326,13 +2326,13 @@
         <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4784</v>
+        <v>1.0624</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6528</v>
+        <v>0.8887</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1744</v>
+        <v>0.1737</v>
       </c>
       <c r="V24" t="n">
         <v>-0.7886</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.7104</v>
+        <v>-3.5196</v>
       </c>
       <c r="E25" t="n">
         <v>-2.4926</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2178</v>
+        <v>-1.027</v>
       </c>
       <c r="G25" t="n">
         <v>-1.2689</v>
@@ -2404,13 +2404,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2095</v>
+        <v>-0.0187</v>
       </c>
       <c r="T25" t="n">
         <v>0.2399</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4494</v>
+        <v>-0.2585</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>7.1114</v>
+        <v>11.0432</v>
       </c>
       <c r="E26" t="n">
-        <v>8.901199999999999</v>
+        <v>8.901200000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.79</v>
+        <v>2.1418</v>
       </c>
       <c r="G26" t="n">
         <v>4.5602</v>
@@ -2455,16 +2455,16 @@
         <v>-4.4668</v>
       </c>
       <c r="J26" t="n">
-        <v>4.274300000000001</v>
+        <v>4.274299999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>4.492999999999999</v>
+        <v>4.493</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.2185</v>
+        <v>-0.2185000000000002</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2858999999999998</v>
+        <v>0.2858999999999999</v>
       </c>
       <c r="N26" t="n">
         <v>4.5342</v>
@@ -2482,13 +2482,13 @@
         <v>12.7575</v>
       </c>
       <c r="S26" t="n">
-        <v>6.172099999999999</v>
+        <v>10.1039</v>
       </c>
       <c r="T26" t="n">
-        <v>11.4042</v>
+        <v>11.4043</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.231999999999999</v>
+        <v>-1.3001</v>
       </c>
       <c r="V26" t="n">
         <v>-0.1417999999999997</v>
